--- a/artfynd/A 60038-2021 artfynd.xlsx
+++ b/artfynd/A 60038-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60038-2021 artfynd.xlsx
+++ b/artfynd/A 60038-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97001174</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646836.8366749721</v>
+        <v>646837</v>
       </c>
       <c r="R2" t="n">
-        <v>6651047.56920906</v>
+        <v>6651048</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -823,12 +808,7 @@
         <v>97001218</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -863,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646817.2992966139</v>
+        <v>646817</v>
       </c>
       <c r="R3" t="n">
-        <v>6651084.381025766</v>
+        <v>6651084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,19 +876,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -968,16 +938,11 @@
         <v>97000967</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -990,12 +955,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1008,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646812.752473174</v>
+        <v>646813</v>
       </c>
       <c r="R4" t="n">
-        <v>6650895.750518511</v>
+        <v>6650896</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,19 +1006,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1110,15 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97000927</v>
+        <v>97001274</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,21 +1076,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1151,7 +1101,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1162,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646834.0967253495</v>
+        <v>646720</v>
       </c>
       <c r="R5" t="n">
-        <v>6650864.020725635</v>
+        <v>6651142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,19 +1145,9 @@
           <t>2021-10-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,7 +1162,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ängsblandskog</t>
+          <t>Lövskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Mossan växer både på trädet och på stenblock intill.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Populus tremula # Mossan växer både på trädet och på stenblock intill.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,6 +1202,125 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97000927</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vaxmyragrytet, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>646834</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6650864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ärentuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
